--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -518,6 +518,9 @@
       <c r="C11" t="str">
         <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -576,7 +579,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101510151035100</v>
+        <v>0101015101510351010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -522,9 +522,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -579,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101015101510351010</v>
+        <v>01010151015103510101010128104201180</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -604,6 +604,9 @@
       <c r="C21" t="str">
         <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -662,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010151015103510101010128104201180</v>
+        <v>010101510151035101010101281042011815</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,9 +608,92 @@
         <v>15</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>476_酸浆果_Physalis_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>706_小西瓜挂_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -665,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101510151035101010101281042011815</v>
+        <v>0101015101510351010101012810420118151010105501010560</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -690,6 +690,9 @@
       <c r="A31" t="str">
         <v>6</v>
       </c>
+      <c r="C31" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -693,6 +693,9 @@
       <c r="C31" t="str">
         <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -751,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101015101510351010101012810420118151010105501010560</v>
+        <v>01010151015103510101010128104201181510101055010105612</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,9 +697,74 @@
         <v>12</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>7</v>
+      </c>
+      <c r="C35" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>8</v>
+      </c>
+      <c r="C36" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>9</v>
+      </c>
+      <c r="C37" t="str">
+        <v>834_海芋黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -754,7 +819,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010151015103510101010128104201181510101055010105612</v>
+        <v>01010151015103510101010128104201181510101055010105612377101033</v>
       </c>
     </row>
   </sheetData>
